--- a/output/Sunset/TestEnvData.xlsx
+++ b/output/Sunset/TestEnvData.xlsx
@@ -726,19 +726,19 @@
         <v>06/01/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>06/02/2025</v>
+        <v>06/03/2025</v>
       </c>
       <c r="C2" t="str">
-        <v>$239.00</v>
+        <v>$132.43</v>
       </c>
       <c r="D2" t="str">
-        <v>$239.00</v>
+        <v>$132.43</v>
       </c>
       <c r="E2" t="str">
-        <v>FLCC 05/29/2025</v>
+        <v>Humana 05/31/2025</v>
       </c>
       <c r="F2" t="str">
-        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
+        <v>HMPHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G2" t="str">
         <v>Exact</v>
@@ -752,13 +752,13 @@
         <v>06/03/2025</v>
       </c>
       <c r="C3" t="str">
-        <v>$8,724.37</v>
+        <v>$176.98</v>
       </c>
       <c r="D3" t="str">
-        <v>$8,724.37</v>
+        <v>$176.98</v>
       </c>
       <c r="E3" t="str">
-        <v>HUMANA INC. 05/30/2025</v>
+        <v>HUMANA INC. 05/29/2025</v>
       </c>
       <c r="F3" t="str">
         <v>HMPHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
@@ -772,19 +772,19 @@
         <v>06/01/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>06/03/2025</v>
+        <v>06/02/2025</v>
       </c>
       <c r="C4" t="str">
-        <v>$176.98</v>
+        <v>$239.00</v>
       </c>
       <c r="D4" t="str">
-        <v>$176.98</v>
+        <v>$239.00</v>
       </c>
       <c r="E4" t="str">
-        <v>HUMANA INC. 05/29/2025</v>
+        <v>FLCC 05/29/2025</v>
       </c>
       <c r="F4" t="str">
-        <v>HMPHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G4" t="str">
         <v>Exact</v>
@@ -795,19 +795,19 @@
         <v>06/01/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>06/03/2025</v>
+        <v>06/06/2025</v>
       </c>
       <c r="C5" t="str">
-        <v>$132.43</v>
+        <v>$268.39</v>
       </c>
       <c r="D5" t="str">
-        <v>$132.43</v>
+        <v>$268.39</v>
       </c>
       <c r="E5" t="str">
-        <v>Humana 05/31/2025</v>
+        <v>Epay Zunta Import-256375</v>
       </c>
       <c r="F5" t="str">
-        <v>HMPHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>ZUNTAMERC DEP RECIPIENT</v>
       </c>
       <c r="G5" t="str">
         <v>Exact</v>
@@ -841,19 +841,19 @@
         <v>06/01/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>06/06/2025</v>
+        <v>06/03/2025</v>
       </c>
       <c r="C7" t="str">
-        <v>$268.39</v>
+        <v>$8,724.37</v>
       </c>
       <c r="D7" t="str">
-        <v>$268.39</v>
+        <v>$8,724.37</v>
       </c>
       <c r="E7" t="str">
-        <v>Epay Zunta Import-256375</v>
+        <v>HUMANA INC. 05/30/2025</v>
       </c>
       <c r="F7" t="str">
-        <v>ZUNTAMERC DEP RECIPIENT</v>
+        <v>HMPHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G7" t="str">
         <v>Exact</v>
@@ -910,19 +910,19 @@
         <v>06/02/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>06/02/2025</v>
+        <v>06/03/2025</v>
       </c>
       <c r="C10" t="str">
-        <v>$29,108.00</v>
+        <v>$10,005.89</v>
       </c>
       <c r="D10" t="str">
-        <v>$29,108.00</v>
+        <v>$10,005.89</v>
       </c>
       <c r="E10" t="str">
-        <v>UHC 06/02/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/02/2025</v>
       </c>
       <c r="F10" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\SUNSET LAKE HEALTHCARE</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G10" t="str">
         <v>Exact</v>
@@ -933,19 +933,19 @@
         <v>06/02/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>06/03/2025</v>
+        <v>06/02/2025</v>
       </c>
       <c r="C11" t="str">
-        <v>$10,005.89</v>
+        <v>$29,108.00</v>
       </c>
       <c r="D11" t="str">
-        <v>$10,005.89</v>
+        <v>$29,108.00</v>
       </c>
       <c r="E11" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/02/2025</v>
+        <v>UHC 06/02/2025</v>
       </c>
       <c r="F11" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G11" t="str">
         <v>Exact</v>
@@ -1002,19 +1002,19 @@
         <v>06/04/2025</v>
       </c>
       <c r="B14" t="str">
-        <v>06/09/2025</v>
+        <v>06/05/2025</v>
       </c>
       <c r="C14" t="str">
-        <v>$102,927.81</v>
+        <v>$24,396.05</v>
       </c>
       <c r="D14" t="str">
-        <v>$102,927.81</v>
+        <v>$24,396.05</v>
       </c>
       <c r="E14" t="str">
-        <v>HUMANA INC. 06/04/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/04/2025</v>
       </c>
       <c r="F14" t="str">
-        <v>HMPHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G14" t="str">
         <v>Exact</v>
@@ -1025,19 +1025,19 @@
         <v>06/04/2025</v>
       </c>
       <c r="B15" t="str">
-        <v>06/05/2025</v>
+        <v>06/09/2025</v>
       </c>
       <c r="C15" t="str">
-        <v>$24,396.05</v>
+        <v>$102,927.81</v>
       </c>
       <c r="D15" t="str">
-        <v>$24,396.05</v>
+        <v>$102,927.81</v>
       </c>
       <c r="E15" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/04/2025</v>
+        <v>HUMANA INC. 06/04/2025</v>
       </c>
       <c r="F15" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
+        <v>HMPHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G15" t="str">
         <v>Exact</v>
@@ -1048,19 +1048,19 @@
         <v>06/05/2025</v>
       </c>
       <c r="B16" t="str">
-        <v>06/05/2025</v>
+        <v>06/06/2025</v>
       </c>
       <c r="C16" t="str">
-        <v>$8,952.36</v>
+        <v>$565.02</v>
       </c>
       <c r="D16" t="str">
-        <v>$8,952.36</v>
+        <v>$565.02</v>
       </c>
       <c r="E16" t="str">
-        <v>Epay Zunta Import-255235</v>
+        <v>WPS GHA - MAC J5 PART A 06/05/2025</v>
       </c>
       <c r="F16" t="str">
-        <v>MERCHPAYOUT SVT ZUNTAZUNTASUNSET LAKE HEALTHCARE</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G16" t="str">
         <v>Exact</v>
@@ -1071,19 +1071,19 @@
         <v>06/05/2025</v>
       </c>
       <c r="B17" t="str">
-        <v>06/06/2025</v>
+        <v>06/05/2025</v>
       </c>
       <c r="C17" t="str">
-        <v>$565.02</v>
+        <v>$8,952.36</v>
       </c>
       <c r="D17" t="str">
-        <v>$565.02</v>
+        <v>$8,952.36</v>
       </c>
       <c r="E17" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/05/2025</v>
+        <v>Epay Zunta Import-255235</v>
       </c>
       <c r="F17" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
+        <v>MERCHPAYOUT SVT ZUNTAZUNTASUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G17" t="str">
         <v>Exact</v>
@@ -1117,19 +1117,19 @@
         <v>06/06/2025</v>
       </c>
       <c r="B19" t="str">
-        <v>06/09/2025</v>
+        <v>06/06/2025</v>
       </c>
       <c r="C19" t="str">
-        <v>$2,861.64</v>
+        <v>$1,115.00</v>
       </c>
       <c r="D19" t="str">
-        <v>$2,861.64</v>
+        <v>$1,115.00</v>
       </c>
       <c r="E19" t="str">
-        <v>Epay Zunta Import-257023</v>
+        <v>RFMS 06/06/2025</v>
       </c>
       <c r="F19" t="str">
-        <v>MERCHPAYOUT SVT ZUNTAZUNTASUNSET LAKE HEALTHCARE</v>
+        <v>NATIONAL DATA CRT#FC WDL RECORD #</v>
       </c>
       <c r="G19" t="str">
         <v>Exact</v>
@@ -1140,19 +1140,19 @@
         <v>06/06/2025</v>
       </c>
       <c r="B20" t="str">
-        <v>06/06/2025</v>
+        <v>06/09/2025</v>
       </c>
       <c r="C20" t="str">
-        <v>$1,115.00</v>
+        <v>$2,861.64</v>
       </c>
       <c r="D20" t="str">
-        <v>$1,115.00</v>
+        <v>$2,861.64</v>
       </c>
       <c r="E20" t="str">
-        <v>RFMS 06/06/2025</v>
+        <v>Epay Zunta Import-257023</v>
       </c>
       <c r="F20" t="str">
-        <v>NATIONAL DATA CRT#FC WDL RECORD #</v>
+        <v>MERCHPAYOUT SVT ZUNTAZUNTASUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G20" t="str">
         <v>Exact</v>
@@ -1232,19 +1232,19 @@
         <v>06/10/2025</v>
       </c>
       <c r="B24" t="str">
-        <v>06/11/2025</v>
+        <v>06/10/2025</v>
       </c>
       <c r="C24" t="str">
-        <v>$2,965.80</v>
+        <v>$250.00</v>
       </c>
       <c r="D24" t="str">
-        <v>$2,965.80</v>
+        <v>$250.00</v>
       </c>
       <c r="E24" t="str">
-        <v>FLORIDA BLUE 06/10/2025</v>
+        <v>Epay Zunta Import-257965</v>
       </c>
       <c r="F24" t="str">
-        <v>BCBSF HCCLAIMPMT *\</v>
+        <v>ZUNTAMERC DEP RECIPIENT</v>
       </c>
       <c r="G24" t="str">
         <v>Exact</v>
@@ -1258,16 +1258,16 @@
         <v>06/10/2025</v>
       </c>
       <c r="C25" t="str">
-        <v>$80,623.69</v>
+        <v>$1,033.22</v>
       </c>
       <c r="D25" t="str">
-        <v>$80,623.69</v>
+        <v>$1,033.22</v>
       </c>
       <c r="E25" t="str">
-        <v>Florida Community 06/06/2025</v>
+        <v>SIMPLY HEALTHCARE PLANS 06/10/2025</v>
       </c>
       <c r="F25" t="str">
-        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
+        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G25" t="str">
         <v>Exact</v>
@@ -1278,19 +1278,19 @@
         <v>06/10/2025</v>
       </c>
       <c r="B26" t="str">
-        <v>06/10/2025</v>
+        <v>06/11/2025</v>
       </c>
       <c r="C26" t="str">
-        <v>$1,033.22</v>
+        <v>$2,745.75</v>
       </c>
       <c r="D26" t="str">
-        <v>$1,033.22</v>
+        <v>$2,745.75</v>
       </c>
       <c r="E26" t="str">
-        <v>SIMPLY HEALTHCARE PLANS 06/10/2025</v>
+        <v>Sunshine Health 06/10/2025</v>
       </c>
       <c r="F26" t="str">
-        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G26" t="str">
         <v>Exact</v>
@@ -1304,16 +1304,16 @@
         <v>06/11/2025</v>
       </c>
       <c r="C27" t="str">
-        <v>$2,745.75</v>
+        <v>$2,965.80</v>
       </c>
       <c r="D27" t="str">
-        <v>$2,745.75</v>
+        <v>$2,965.80</v>
       </c>
       <c r="E27" t="str">
-        <v>Sunshine Health 06/10/2025</v>
+        <v>FLORIDA BLUE 06/10/2025</v>
       </c>
       <c r="F27" t="str">
-        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>BCBSF HCCLAIMPMT *\</v>
       </c>
       <c r="G27" t="str">
         <v>Exact</v>
@@ -1327,16 +1327,16 @@
         <v>06/10/2025</v>
       </c>
       <c r="C28" t="str">
-        <v>$250.00</v>
+        <v>$80,623.69</v>
       </c>
       <c r="D28" t="str">
-        <v>$250.00</v>
+        <v>$80,623.69</v>
       </c>
       <c r="E28" t="str">
-        <v>Epay Zunta Import-257965</v>
+        <v>Florida Community 06/06/2025</v>
       </c>
       <c r="F28" t="str">
-        <v>ZUNTAMERC DEP RECIPIENT</v>
+        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G28" t="str">
         <v>Exact</v>
@@ -1347,19 +1347,19 @@
         <v>06/11/2025</v>
       </c>
       <c r="B29" t="str">
-        <v>06/12/2025</v>
+        <v>06/11/2025</v>
       </c>
       <c r="C29" t="str">
-        <v>$1,470.92</v>
+        <v>$992.44</v>
       </c>
       <c r="D29" t="str">
-        <v>$1,470.92</v>
+        <v>$992.44</v>
       </c>
       <c r="E29" t="str">
-        <v>STATE OF FLORIDA MEDICAID 06/11/2025</v>
+        <v>RFMS 06/11/2025</v>
       </c>
       <c r="F29" t="str">
-        <v>ACH MEDICAIDHCCLAIMPMT TRN***~SUNSET LAKE HEALTHCARE</v>
+        <v>NATIONAL DATA CRT#BC WDL RECORD #</v>
       </c>
       <c r="G29" t="str">
         <v>Exact</v>
@@ -1373,13 +1373,13 @@
         <v>06/11/2025</v>
       </c>
       <c r="C30" t="str">
-        <v>$8,250.00</v>
+        <v>$1,406.25</v>
       </c>
       <c r="D30" t="str">
-        <v>$8,250.00</v>
+        <v>$1,406.25</v>
       </c>
       <c r="E30" t="str">
-        <v>Aetna/Coventry PPO - MGD MCR 06/11/2025</v>
+        <v>Aetna/Coventry - Commercial 06/11/2025</v>
       </c>
       <c r="F30" t="str">
         <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
@@ -1393,19 +1393,19 @@
         <v>06/11/2025</v>
       </c>
       <c r="B31" t="str">
-        <v>06/11/2025</v>
+        <v>06/12/2025</v>
       </c>
       <c r="C31" t="str">
-        <v>$1,406.25</v>
+        <v>$1,470.92</v>
       </c>
       <c r="D31" t="str">
-        <v>$1,406.25</v>
+        <v>$1,470.92</v>
       </c>
       <c r="E31" t="str">
-        <v>Aetna/Coventry - Commercial 06/11/2025</v>
+        <v>STATE OF FLORIDA MEDICAID 06/11/2025</v>
       </c>
       <c r="F31" t="str">
-        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>ACH MEDICAIDHCCLAIMPMT TRN***~SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G31" t="str">
         <v>Exact</v>
@@ -1419,16 +1419,16 @@
         <v>06/11/2025</v>
       </c>
       <c r="C32" t="str">
-        <v>$992.44</v>
+        <v>$2,386.00</v>
       </c>
       <c r="D32" t="str">
-        <v>$992.44</v>
+        <v>$2,386.00</v>
       </c>
       <c r="E32" t="str">
-        <v>RFMS 06/11/2025</v>
+        <v>Epay Zunta Import-258682</v>
       </c>
       <c r="F32" t="str">
-        <v>NATIONAL DATA CRT#BC WDL RECORD #</v>
+        <v>ZUNTAMERC DEP RECIPIENT</v>
       </c>
       <c r="G32" t="str">
         <v>Exact</v>
@@ -1442,16 +1442,16 @@
         <v>06/11/2025</v>
       </c>
       <c r="C33" t="str">
-        <v>$8,519.75</v>
+        <v>$5,742.75</v>
       </c>
       <c r="D33" t="str">
-        <v>$8,519.75</v>
+        <v>$5,742.75</v>
       </c>
       <c r="E33" t="str">
-        <v>SIMPLY HEALTHCARE PLANS 06/11/2025</v>
+        <v>Sunshine Health 06/11/2025</v>
       </c>
       <c r="F33" t="str">
-        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G33" t="str">
         <v>Exact</v>
@@ -1465,16 +1465,16 @@
         <v>06/11/2025</v>
       </c>
       <c r="C34" t="str">
-        <v>$5,742.75</v>
+        <v>$8,250.00</v>
       </c>
       <c r="D34" t="str">
-        <v>$5,742.75</v>
+        <v>$8,250.00</v>
       </c>
       <c r="E34" t="str">
-        <v>Sunshine Health 06/11/2025</v>
+        <v>Aetna/Coventry PPO - MGD MCR 06/11/2025</v>
       </c>
       <c r="F34" t="str">
-        <v>SUNSHINE STATE HHCCLAIMPMTTRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G34" t="str">
         <v>Exact</v>
@@ -1488,43 +1488,42 @@
         <v>06/11/2025</v>
       </c>
       <c r="C35" t="str">
-        <v>$2,386.00</v>
+        <v>$8,519.75</v>
       </c>
       <c r="D35" t="str">
-        <v>$2,386.00</v>
+        <v>$8,519.75</v>
       </c>
       <c r="E35" t="str">
-        <v>Epay Zunta Import-258682</v>
+        <v>SIMPLY HEALTHCARE PLANS 06/11/2025</v>
       </c>
       <c r="F35" t="str">
-        <v>ZUNTAMERC DEP RECIPIENT</v>
+        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G35" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="36" xml:space="preserve">
+    <row r="36">
       <c r="A36" t="str">
         <v>06/12/2025</v>
       </c>
       <c r="B36" t="str">
-        <v>06/12/2025</v>
+        <v>06/13/2025</v>
       </c>
       <c r="C36" t="str">
-        <v>$22,355.91</v>
+        <v>$1,596.04</v>
       </c>
       <c r="D36" t="str">
-        <v>$22,355.91</v>
+        <v>$1,596.04</v>
       </c>
       <c r="E36" t="str">
-        <v>Deposit 06/12/2025</v>
-      </c>
-      <c r="F36" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $13,458.75 (Sunset Lake Settlement | 6/12)
-2: $8,897.16 (Sunset Lake Settlement | 6/12)</v>
+        <v>Deposit 6/12/2025</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Sunset Lake Settlement</v>
       </c>
       <c r="G36" t="str">
-        <v>One-to-Many</v>
+        <v>Exact</v>
       </c>
     </row>
     <row r="37">
@@ -1578,19 +1577,19 @@
         <v>06/12/2025</v>
       </c>
       <c r="B39" t="str">
-        <v>06/12/2025</v>
+        <v>06/13/2025</v>
       </c>
       <c r="C39" t="str">
-        <v>$17,677.50</v>
+        <v>$12,630.84</v>
       </c>
       <c r="D39" t="str">
-        <v>$17,677.50</v>
+        <v>$12,630.84</v>
       </c>
       <c r="E39" t="str">
-        <v>SIMPLY HEALTHCARE PLANS 06/12/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/12/2025</v>
       </c>
       <c r="F39" t="str">
-        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G39" t="str">
         <v>Exact</v>
@@ -1601,45 +1600,46 @@
         <v>06/12/2025</v>
       </c>
       <c r="B40" t="str">
-        <v>06/13/2025</v>
+        <v>06/12/2025</v>
       </c>
       <c r="C40" t="str">
-        <v>$1,596.04</v>
+        <v>$17,677.50</v>
       </c>
       <c r="D40" t="str">
-        <v>$1,596.04</v>
+        <v>$17,677.50</v>
       </c>
       <c r="E40" t="str">
-        <v>Deposit 6/12/2025</v>
+        <v>SIMPLY HEALTHCARE PLANS 06/12/2025</v>
       </c>
       <c r="F40" t="str">
-        <v>Sunset Lake Settlement</v>
+        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G40" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" xml:space="preserve">
       <c r="A41" t="str">
         <v>06/12/2025</v>
       </c>
       <c r="B41" t="str">
-        <v>06/13/2025</v>
+        <v>06/12/2025</v>
       </c>
       <c r="C41" t="str">
-        <v>$12,630.84</v>
+        <v>$22,355.91</v>
       </c>
       <c r="D41" t="str">
-        <v>$12,630.84</v>
+        <v>$22,355.91</v>
       </c>
       <c r="E41" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/12/2025</v>
-      </c>
-      <c r="F41" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
+        <v>Deposit 06/12/2025</v>
+      </c>
+      <c r="F41" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $13,458.75 (Sunset Lake Settlement | 6/12)
+2: $8,897.16 (Sunset Lake Settlement | 6/12)</v>
       </c>
       <c r="G41" t="str">
-        <v>Exact</v>
+        <v>One-to-Many</v>
       </c>
     </row>
     <row r="42">
@@ -1742,16 +1742,16 @@
         <v>06/16/2025</v>
       </c>
       <c r="C46" t="str">
-        <v>$10,800.00</v>
+        <v>$1,000.00</v>
       </c>
       <c r="D46" t="str">
-        <v>$10,800.00</v>
+        <v>$1,000.00</v>
       </c>
       <c r="E46" t="str">
-        <v>Aetna/Coventry PPO - MGD MCR 06/16/2025</v>
+        <v>Epay Zunta Import-260563 (1)</v>
       </c>
       <c r="F46" t="str">
-        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>ZUNTAMERC DEP RECIPIENT</v>
       </c>
       <c r="G46" t="str">
         <v>Exact</v>
@@ -1788,16 +1788,16 @@
         <v>06/16/2025</v>
       </c>
       <c r="C48" t="str">
-        <v>$1,000.00</v>
+        <v>$10,800.00</v>
       </c>
       <c r="D48" t="str">
-        <v>$1,000.00</v>
+        <v>$10,800.00</v>
       </c>
       <c r="E48" t="str">
-        <v>Epay Zunta Import-260563 (1)</v>
+        <v>Aetna/Coventry PPO - MGD MCR 06/16/2025</v>
       </c>
       <c r="F48" t="str">
-        <v>ZUNTAMERC DEP RECIPIENT</v>
+        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G48" t="str">
         <v>Exact</v>
@@ -1811,16 +1811,16 @@
         <v>06/17/2025</v>
       </c>
       <c r="C49" t="str">
-        <v>$11,625.00</v>
+        <v>$1,286.01</v>
       </c>
       <c r="D49" t="str">
-        <v>$11,625.00</v>
+        <v>$1,286.01</v>
       </c>
       <c r="E49" t="str">
-        <v>Aetna/Coventry PPO - MGD MCR 06/17/2025</v>
+        <v>Epay Zunta Import-260853</v>
       </c>
       <c r="F49" t="str">
-        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>ZUNTAMERC DEP RECIPIENT</v>
       </c>
       <c r="G49" t="str">
         <v>Exact</v>
@@ -1857,16 +1857,16 @@
         <v>06/17/2025</v>
       </c>
       <c r="C51" t="str">
-        <v>$21,252.00</v>
+        <v>$11,625.00</v>
       </c>
       <c r="D51" t="str">
-        <v>$21,252.00</v>
+        <v>$11,625.00</v>
       </c>
       <c r="E51" t="str">
-        <v>UHC 06/13/2025</v>
+        <v>Aetna/Coventry PPO - MGD MCR 06/17/2025</v>
       </c>
       <c r="F51" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\SUNSET LAKE HEALTHCARE</v>
+        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G51" t="str">
         <v>Exact</v>
@@ -1880,16 +1880,16 @@
         <v>06/17/2025</v>
       </c>
       <c r="C52" t="str">
-        <v>$1,286.01</v>
+        <v>$21,252.00</v>
       </c>
       <c r="D52" t="str">
-        <v>$1,286.01</v>
+        <v>$21,252.00</v>
       </c>
       <c r="E52" t="str">
-        <v>Epay Zunta Import-260853</v>
+        <v>UHC 06/13/2025</v>
       </c>
       <c r="F52" t="str">
-        <v>ZUNTAMERC DEP RECIPIENT</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G52" t="str">
         <v>Exact</v>
@@ -1900,19 +1900,19 @@
         <v>06/18/2025</v>
       </c>
       <c r="B53" t="str">
-        <v>06/18/2025</v>
+        <v>06/23/2025</v>
       </c>
       <c r="C53" t="str">
-        <v>$5,237.50</v>
+        <v>$613.00</v>
       </c>
       <c r="D53" t="str">
-        <v>$5,237.50</v>
+        <v>$613.00</v>
       </c>
       <c r="E53" t="str">
-        <v>AARP SUPPLEMENTAL HEALTH PLANS FROM UNITEDHEALTHCARE 06/18/2025</v>
+        <v>UHC 06/18/2025</v>
       </c>
       <c r="F53" t="str">
-        <v>AARP SUPPLEMENTAHCCLAIMPMT TRN****\SUNSET LAKE HEALTHCARE</v>
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G53" t="str">
         <v>Exact</v>
@@ -1926,16 +1926,16 @@
         <v>06/18/2025</v>
       </c>
       <c r="C54" t="str">
-        <v>$9,375.00</v>
+        <v>$5,237.50</v>
       </c>
       <c r="D54" t="str">
-        <v>$9,375.00</v>
+        <v>$5,237.50</v>
       </c>
       <c r="E54" t="str">
-        <v>AETNA 06/18/2025</v>
+        <v>AARP SUPPLEMENTAL HEALTH PLANS FROM UNITEDHEALTHCARE 06/18/2025</v>
       </c>
       <c r="F54" t="str">
-        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>AARP SUPPLEMENTAHCCLAIMPMT TRN****\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G54" t="str">
         <v>Exact</v>
@@ -1946,19 +1946,19 @@
         <v>06/18/2025</v>
       </c>
       <c r="B55" t="str">
-        <v>06/20/2025</v>
+        <v>06/18/2025</v>
       </c>
       <c r="C55" t="str">
-        <v>$30,782.73</v>
+        <v>$9,375.00</v>
       </c>
       <c r="D55" t="str">
-        <v>$30,782.73</v>
+        <v>$9,375.00</v>
       </c>
       <c r="E55" t="str">
-        <v>WELLMED MEDICAL MANAGEMENT, INC. 06/18/2025</v>
+        <v>AETNA 06/18/2025</v>
       </c>
       <c r="F55" t="str">
-        <v>HNB - ECHO HCCLAIMPMT TRN***\ SUNSET LAKE HEALTHCARE</v>
+        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G55" t="str">
         <v>Exact</v>
@@ -1969,19 +1969,19 @@
         <v>06/18/2025</v>
       </c>
       <c r="B56" t="str">
-        <v>06/23/2025</v>
+        <v>06/20/2025</v>
       </c>
       <c r="C56" t="str">
-        <v>$613.00</v>
+        <v>$26,157.99</v>
       </c>
       <c r="D56" t="str">
-        <v>$613.00</v>
+        <v>$26,157.99</v>
       </c>
       <c r="E56" t="str">
-        <v>UHC 06/18/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/18/2025</v>
       </c>
       <c r="F56" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**B**\SUNSET LAKE HEALTHCARE</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G56" t="str">
         <v>Exact</v>
@@ -1995,16 +1995,16 @@
         <v>06/20/2025</v>
       </c>
       <c r="C57" t="str">
-        <v>$26,157.99</v>
+        <v>$30,782.73</v>
       </c>
       <c r="D57" t="str">
-        <v>$26,157.99</v>
+        <v>$30,782.73</v>
       </c>
       <c r="E57" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/18/2025</v>
+        <v>WELLMED MEDICAL MANAGEMENT, INC. 06/18/2025</v>
       </c>
       <c r="F57" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
+        <v>HNB - ECHO HCCLAIMPMT TRN***\ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G57" t="str">
         <v>Exact</v>
@@ -2039,19 +2039,19 @@
         <v>06/20/2025</v>
       </c>
       <c r="B59" t="str">
-        <v>06/20/2025</v>
+        <v>06/24/2025</v>
       </c>
       <c r="C59" t="str">
-        <v>$2,625.00</v>
+        <v>$239.00</v>
       </c>
       <c r="D59" t="str">
-        <v>$2,625.00</v>
+        <v>$239.00</v>
       </c>
       <c r="E59" t="str">
-        <v>AETNA 06/20/2025</v>
+        <v>FLCC 06/20/2025</v>
       </c>
       <c r="F59" t="str">
-        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G59" t="str">
         <v>Exact</v>
@@ -2062,19 +2062,19 @@
         <v>06/20/2025</v>
       </c>
       <c r="B60" t="str">
-        <v>06/24/2025</v>
+        <v>06/20/2025</v>
       </c>
       <c r="C60" t="str">
-        <v>$239.00</v>
+        <v>$2,625.00</v>
       </c>
       <c r="D60" t="str">
-        <v>$239.00</v>
+        <v>$2,625.00</v>
       </c>
       <c r="E60" t="str">
-        <v>FLCC 06/20/2025</v>
+        <v>AETNA 06/20/2025</v>
       </c>
       <c r="F60" t="str">
-        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
+        <v>AETNA ASHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G60" t="str">
         <v>Exact</v>
@@ -2154,19 +2154,19 @@
         <v>06/24/2025</v>
       </c>
       <c r="B64" t="str">
-        <v>06/25/2025</v>
+        <v>06/24/2025</v>
       </c>
       <c r="C64" t="str">
-        <v>$9,110.00</v>
+        <v>$129.23</v>
       </c>
       <c r="D64" t="str">
-        <v>$9,110.00</v>
+        <v>$129.23</v>
       </c>
       <c r="E64" t="str">
-        <v>FLORIDA BLUE 06/24/2025</v>
+        <v>SIMPLY HEALTHCARE PLANS 06/24/2025</v>
       </c>
       <c r="F64" t="str">
-        <v>BCBSF HCCLAIMPMT *\</v>
+        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G64" t="str">
         <v>Exact</v>
@@ -2177,19 +2177,19 @@
         <v>06/24/2025</v>
       </c>
       <c r="B65" t="str">
-        <v>06/24/2025</v>
+        <v>06/25/2025</v>
       </c>
       <c r="C65" t="str">
-        <v>$129.23</v>
+        <v>$9,110.00</v>
       </c>
       <c r="D65" t="str">
-        <v>$129.23</v>
+        <v>$9,110.00</v>
       </c>
       <c r="E65" t="str">
-        <v>SIMPLY HEALTHCARE PLANS 06/24/2025</v>
+        <v>FLORIDA BLUE 06/24/2025</v>
       </c>
       <c r="F65" t="str">
-        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>BCBSF HCCLAIMPMT *\</v>
       </c>
       <c r="G65" t="str">
         <v>Exact</v>
@@ -2200,19 +2200,19 @@
         <v>06/25/2025</v>
       </c>
       <c r="B66" t="str">
-        <v>06/27/2025</v>
+        <v>06/25/2025</v>
       </c>
       <c r="C66" t="str">
-        <v>$1,410.91</v>
+        <v>$1,272.92</v>
       </c>
       <c r="D66" t="str">
-        <v>$1,410.91</v>
+        <v>$1,272.92</v>
       </c>
       <c r="E66" t="str">
-        <v>Florida Community 06/25/2205</v>
+        <v>SIMPLY HEALTHCARE PLANS 06/25/2025</v>
       </c>
       <c r="F66" t="str">
-        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
+        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G66" t="str">
         <v>Exact</v>
@@ -2223,19 +2223,19 @@
         <v>06/25/2025</v>
       </c>
       <c r="B67" t="str">
-        <v>06/25/2025</v>
+        <v>06/27/2025</v>
       </c>
       <c r="C67" t="str">
-        <v>$6,995.97</v>
+        <v>$1,410.91</v>
       </c>
       <c r="D67" t="str">
-        <v>$6,995.97</v>
+        <v>$1,410.91</v>
       </c>
       <c r="E67" t="str">
-        <v>RFMS 06/25/2025</v>
+        <v>Florida Community 06/25/2205</v>
       </c>
       <c r="F67" t="str">
-        <v>NATIONAL DATA CRT#AC WDL RECORD #</v>
+        <v>FLORIDA COMMUNI HCCLAIMPMT TRN**-**FCCP~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G67" t="str">
         <v>Exact</v>
@@ -2249,16 +2249,16 @@
         <v>06/25/2025</v>
       </c>
       <c r="C68" t="str">
-        <v>$1,272.92</v>
+        <v>$6,995.97</v>
       </c>
       <c r="D68" t="str">
-        <v>$1,272.92</v>
+        <v>$6,995.97</v>
       </c>
       <c r="E68" t="str">
-        <v>SIMPLY HEALTHCARE PLANS 06/25/2025</v>
+        <v>RFMS 06/25/2025</v>
       </c>
       <c r="F68" t="str">
-        <v>SIMPLY FLCHCCLAIMPMT TRN***\SUNSET LAKE HEALTHCARE</v>
+        <v>NATIONAL DATA CRT#AC WDL RECORD #</v>
       </c>
       <c r="G68" t="str">
         <v>Exact</v>
@@ -2287,29 +2287,27 @@
         <v>Exact</v>
       </c>
     </row>
-    <row r="70" xml:space="preserve">
+    <row r="70">
       <c r="A70" t="str">
         <v>06/27/2025</v>
       </c>
       <c r="B70" t="str">
-        <v>06/30/2025</v>
+        <v>06/27/2025</v>
       </c>
       <c r="C70" t="str">
-        <v>$20,843.35</v>
+        <v>$880.00</v>
       </c>
       <c r="D70" t="str">
-        <v>$20,843.35</v>
-      </c>
-      <c r="E70" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $9,878.10 (Deposit 06/27/2025 part 1 | 6/27)
-2: $10,965.25 (Deposit 06/27/2025 WB#5508 part 2 | 6/27)</v>
-      </c>
-      <c r="F70" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $15,585.54 (Sunset Lake Settlement | 6/30)
-2: $5,257.81 (Sunset Lake Settlement | 6/30)</v>
+        <v>$880.00</v>
+      </c>
+      <c r="E70" t="str">
+        <v>UHC 06/27/2025</v>
+      </c>
+      <c r="F70" t="str">
+        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G70" t="str">
-        <v>Many-to-Many</v>
+        <v>Exact</v>
       </c>
     </row>
     <row r="71">
@@ -2340,25 +2338,25 @@
         <v>06/27/2025</v>
       </c>
       <c r="B72" t="str">
-        <v>06/27/2025</v>
+        <v>06/30/2025</v>
       </c>
       <c r="C72" t="str">
-        <v>$880.00</v>
+        <v>$4,478.73</v>
       </c>
       <c r="D72" t="str">
-        <v>$880.00</v>
+        <v>$4,478.73</v>
       </c>
       <c r="E72" t="str">
-        <v>UHC 06/27/2025</v>
+        <v>WPS GHA - MAC J5 PART A 06/27/2025</v>
       </c>
       <c r="F72" t="str">
-        <v>UNITEDHEALTHCAREHCCLAIMPMT TRN**T**\SUNSET LAKE HEALTHCARE</v>
+        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
       </c>
       <c r="G72" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" xml:space="preserve">
       <c r="A73" t="str">
         <v>06/27/2025</v>
       </c>
@@ -2366,19 +2364,21 @@
         <v>06/30/2025</v>
       </c>
       <c r="C73" t="str">
-        <v>$4,478.73</v>
+        <v>$20,843.35</v>
       </c>
       <c r="D73" t="str">
-        <v>$4,478.73</v>
-      </c>
-      <c r="E73" t="str">
-        <v>WPS GHA - MAC J5 PART A 06/27/2025</v>
-      </c>
-      <c r="F73" t="str">
-        <v>WISCONSIN PHYSICHCCLAIMPMT TRN**EFT**~ SUNSET LAKE HEALTHCARE</v>
+        <v>$20,843.35</v>
+      </c>
+      <c r="E73" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $9,878.10 (Deposit 06/27/2025 part 1 | 6/27)
+2: $10,965.25 (Deposit 06/27/2025 WB#5508 part 2 | 6/27)</v>
+      </c>
+      <c r="F73" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $15,585.54 (Sunset Lake Settlement | 6/30)
+2: $5,257.81 (Sunset Lake Settlement | 6/30)</v>
       </c>
       <c r="G73" t="str">
-        <v>Exact</v>
+        <v>Many-to-Many</v>
       </c>
     </row>
     <row r="74">
@@ -2588,10 +2588,10 @@
         <v>06/01/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$2,200.00</v>
+        <v>-$2,442.93</v>
       </c>
       <c r="C2" t="str">
-        <v>Batch#2077 - Deposit 11/25/2022 * Correction *</v>
+        <v>Batch#5401 - Deposit 05/22/2025 * Reversals *</v>
       </c>
     </row>
     <row r="3">
@@ -2599,7 +2599,7 @@
         <v>06/01/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>$-2,200.00</v>
+        <v>-$2,200.00</v>
       </c>
       <c r="C3" t="str">
         <v>Batch#2077 - Deposit 11/25/2022 * Reversals *</v>
@@ -2610,10 +2610,10 @@
         <v>06/01/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$2,442.93</v>
+        <v>-$882.00</v>
       </c>
       <c r="C4" t="str">
-        <v>Batch#5401 - Deposit 05/22/2025 * Correction *</v>
+        <v>Batch#5021 - CC 02/23/2025 * Reversals *</v>
       </c>
     </row>
     <row r="5">
@@ -2621,10 +2621,10 @@
         <v>06/01/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$-2,442.93</v>
+        <v>-$417.87</v>
       </c>
       <c r="C5" t="str">
-        <v>Batch#5401 - Deposit 05/22/2025 * Reversals *</v>
+        <v>Batch#5466 - UHC 05/29/2025 * Reversals *</v>
       </c>
     </row>
     <row r="6">
@@ -2643,10 +2643,10 @@
         <v>06/01/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>$-417.87</v>
+        <v>$882.00</v>
       </c>
       <c r="C7" t="str">
-        <v>Batch#5466 - UHC 05/29/2025 * Reversals *</v>
+        <v>Batch#5021 - CC 02/23/2025 * Correction *</v>
       </c>
     </row>
     <row r="8">
@@ -2654,10 +2654,10 @@
         <v>06/01/2025</v>
       </c>
       <c r="B8" t="str">
-        <v>$-882.00</v>
+        <v>$2,200.00</v>
       </c>
       <c r="C8" t="str">
-        <v>Batch#5021 - CC 02/23/2025 * Reversals *</v>
+        <v>Batch#2077 - Deposit 11/25/2022 * Correction *</v>
       </c>
     </row>
     <row r="9">
@@ -2665,10 +2665,10 @@
         <v>06/01/2025</v>
       </c>
       <c r="B9" t="str">
-        <v>$882.00</v>
+        <v>$2,442.93</v>
       </c>
       <c r="C9" t="str">
-        <v>Batch#5021 - CC 02/23/2025 * Correction *</v>
+        <v>Batch#5401 - Deposit 05/22/2025 * Correction *</v>
       </c>
     </row>
     <row r="10">
@@ -2676,10 +2676,10 @@
         <v>06/05/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>$1,006.48</v>
+        <v>-$1,006.48</v>
       </c>
       <c r="C10" t="str">
-        <v>Deposit 06/05/2025</v>
+        <v>Batch#5431 - Deposit 06/05/2025 * Reversals *</v>
       </c>
     </row>
     <row r="11">
@@ -2687,10 +2687,10 @@
         <v>06/05/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>$-1,006.48</v>
+        <v>$1,006.48</v>
       </c>
       <c r="C11" t="str">
-        <v>Batch#5431 - Deposit 06/05/2025 * Reversals *</v>
+        <v>Deposit 06/05/2025</v>
       </c>
     </row>
   </sheetData>
@@ -2726,13 +2726,13 @@
         <v>06/02/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$29,516.00</v>
+        <v>$150.00</v>
       </c>
       <c r="C2" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D2" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
       </c>
       <c r="E2" t="str">
         <v>-</v>
@@ -2760,7 +2760,7 @@
         <v>06/02/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$150.00</v>
+        <v>$300.00</v>
       </c>
       <c r="C4" t="str">
         <v>275 ZBA Credit</v>
@@ -2777,13 +2777,13 @@
         <v>06/02/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$300.00</v>
+        <v>$29,516.00</v>
       </c>
       <c r="C5" t="str">
-        <v>275 ZBA Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D5" t="str">
-        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E5" t="str">
         <v>-</v>
@@ -2845,13 +2845,13 @@
         <v>06/04/2025</v>
       </c>
       <c r="B9" t="str">
-        <v>$55,000.00</v>
+        <v>$9,688.19</v>
       </c>
       <c r="C9" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>206 Book Transfer Credit</v>
       </c>
       <c r="D9" t="str">
-        <v>DBT=A CONNECTONE BANK ENGLEWOOD CLIFFS NJ |BFC=CTR |ORG= VENICE NH LLC RELLA BLVD SUITE MONTEBELLO NY - |OBI=TRANSFER BETWEEN OWN ACCOUNTS |SRF= |BBK=D SUNSET LAKE HEALTHCARE AND REHABILI RELLA BLVD STE SUFFERN NY US |BNF= SUNSET LAKE HEALTHCARE AND REHABILI RELLA BLVD SUITE MONTEBELLO NY |Fed Ref#: MMQFMPBFT |Time Recv:..</v>
+        <v>REF L FUNDS TRANSFER FRMDEP XXXXX FROM</v>
       </c>
       <c r="E9" t="str">
         <v>-</v>
@@ -2862,7 +2862,7 @@
         <v>06/04/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>$9,688.19</v>
+        <v>$10,000.00</v>
       </c>
       <c r="C10" t="str">
         <v>206 Book Transfer Credit</v>
@@ -2879,13 +2879,13 @@
         <v>06/04/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>$10,000.00</v>
+        <v>$55,000.00</v>
       </c>
       <c r="C11" t="str">
-        <v>206 Book Transfer Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D11" t="str">
-        <v>REF L FUNDS TRANSFER FRMDEP XXXXX FROM</v>
+        <v>DBT=A CONNECTONE BANK ENGLEWOOD CLIFFS NJ |BFC=CTR |ORG= VENICE NH LLC RELLA BLVD SUITE MONTEBELLO NY - |OBI=TRANSFER BETWEEN OWN ACCOUNTS |SRF= |BBK=D SUNSET LAKE HEALTHCARE AND REHABILI RELLA BLVD STE SUFFERN NY US |BNF= SUNSET LAKE HEALTHCARE AND REHABILI RELLA BLVD SUITE MONTEBELLO NY |Fed Ref#: MMQFMPBFT |Time Recv:..</v>
       </c>
       <c r="E11" t="str">
         <v>-</v>
@@ -2896,13 +2896,13 @@
         <v>06/05/2025</v>
       </c>
       <c r="B12" t="str">
-        <v>$28,154.01</v>
+        <v>$24,396.05</v>
       </c>
       <c r="C12" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D12" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E12" t="str">
         <v>-</v>
@@ -2913,13 +2913,13 @@
         <v>06/05/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>$50,000.00</v>
+        <v>$28,154.01</v>
       </c>
       <c r="C13" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D13" t="str">
-        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E13" t="str">
         <v>-</v>
@@ -2930,13 +2930,13 @@
         <v>06/05/2025</v>
       </c>
       <c r="B14" t="str">
-        <v>$24,396.05</v>
+        <v>$50,000.00</v>
       </c>
       <c r="C14" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D14" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
       </c>
       <c r="E14" t="str">
         <v>-</v>
@@ -2947,13 +2947,13 @@
         <v>06/06/2025</v>
       </c>
       <c r="B15" t="str">
-        <v>$268.39</v>
+        <v>$38.46</v>
       </c>
       <c r="C15" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D15" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E15" t="str">
         <v>-</v>
@@ -2964,13 +2964,13 @@
         <v>06/06/2025</v>
       </c>
       <c r="B16" t="str">
-        <v>$38.46</v>
+        <v>$268.39</v>
       </c>
       <c r="C16" t="str">
-        <v>275 ZBA Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D16" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E16" t="str">
         <v>-</v>
@@ -3032,13 +3032,13 @@
         <v>06/10/2025</v>
       </c>
       <c r="B20" t="str">
-        <v>$95,000.00</v>
+        <v>$623.69</v>
       </c>
       <c r="C20" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D20" t="str">
-        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E20" t="str">
         <v>-</v>
@@ -3083,13 +3083,13 @@
         <v>06/10/2025</v>
       </c>
       <c r="B23" t="str">
-        <v>$623.69</v>
+        <v>$95,000.00</v>
       </c>
       <c r="C23" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D23" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
       </c>
       <c r="E23" t="str">
         <v>-</v>
@@ -3117,7 +3117,7 @@
         <v>06/11/2025</v>
       </c>
       <c r="B25" t="str">
-        <v>$34,150.50</v>
+        <v>$2,761.66</v>
       </c>
       <c r="C25" t="str">
         <v>201 Individual Automatic Transfer Credit</v>
@@ -3134,13 +3134,13 @@
         <v>06/11/2025</v>
       </c>
       <c r="B26" t="str">
-        <v>$2,761.66</v>
+        <v>$2,965.80</v>
       </c>
       <c r="C26" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D26" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
       </c>
       <c r="E26" t="str">
         <v>-</v>
@@ -3151,13 +3151,13 @@
         <v>06/11/2025</v>
       </c>
       <c r="B27" t="str">
-        <v>$2,965.80</v>
+        <v>$34,150.50</v>
       </c>
       <c r="C27" t="str">
-        <v>275 ZBA Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D27" t="str">
-        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E27" t="str">
         <v>-</v>
@@ -3168,13 +3168,13 @@
         <v>06/12/2025</v>
       </c>
       <c r="B28" t="str">
-        <v>$22,000.00</v>
+        <v>$177.50</v>
       </c>
       <c r="C28" t="str">
-        <v>206 Book Transfer Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D28" t="str">
-        <v>ONLINE XFR FROM: XXXXXX</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E28" t="str">
         <v>-</v>
@@ -3185,7 +3185,7 @@
         <v>06/12/2025</v>
       </c>
       <c r="B29" t="str">
-        <v>$177.50</v>
+        <v>$872.54</v>
       </c>
       <c r="C29" t="str">
         <v>201 Individual Automatic Transfer Credit</v>
@@ -3202,13 +3202,13 @@
         <v>06/12/2025</v>
       </c>
       <c r="B30" t="str">
-        <v>$872.54</v>
+        <v>$22,000.00</v>
       </c>
       <c r="C30" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>206 Book Transfer Credit</v>
       </c>
       <c r="D30" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>ONLINE XFR FROM: XXXXXX</v>
       </c>
       <c r="E30" t="str">
         <v>-</v>
@@ -3253,7 +3253,7 @@
         <v>06/13/2025</v>
       </c>
       <c r="B33" t="str">
-        <v>$9,092.44</v>
+        <v>$881.19</v>
       </c>
       <c r="C33" t="str">
         <v>201 Individual Automatic Transfer Credit</v>
@@ -3270,13 +3270,13 @@
         <v>06/13/2025</v>
       </c>
       <c r="B34" t="str">
-        <v>$12,630.84</v>
+        <v>$1,596.04</v>
       </c>
       <c r="C34" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D34" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
       </c>
       <c r="E34" t="str">
         <v>-</v>
@@ -3287,13 +3287,13 @@
         <v>06/13/2025</v>
       </c>
       <c r="B35" t="str">
-        <v>$881.19</v>
+        <v>$1,596.04</v>
       </c>
       <c r="C35" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D35" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
       </c>
       <c r="E35" t="str">
         <v>-</v>
@@ -3304,13 +3304,13 @@
         <v>06/13/2025</v>
       </c>
       <c r="B36" t="str">
-        <v>$1,596.04</v>
+        <v>$9,092.44</v>
       </c>
       <c r="C36" t="str">
-        <v>275 ZBA Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D36" t="str">
-        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E36" t="str">
         <v>-</v>
@@ -3321,13 +3321,13 @@
         <v>06/13/2025</v>
       </c>
       <c r="B37" t="str">
-        <v>$1,596.04</v>
+        <v>$12,630.84</v>
       </c>
       <c r="C37" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D37" t="str">
-        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E37" t="str">
         <v>-</v>
@@ -3338,7 +3338,7 @@
         <v>06/16/2025</v>
       </c>
       <c r="B38" t="str">
-        <v>$190.15</v>
+        <v>$109.45</v>
       </c>
       <c r="C38" t="str">
         <v>275 ZBA Credit</v>
@@ -3355,13 +3355,13 @@
         <v>06/16/2025</v>
       </c>
       <c r="B39" t="str">
-        <v>$20,200.00</v>
+        <v>$190.15</v>
       </c>
       <c r="C39" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D39" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>ZBA CREDIT - SUB ACCOUNT FROM FROM ACCOUNT</v>
       </c>
       <c r="E39" t="str">
         <v>-</v>
@@ -3389,13 +3389,13 @@
         <v>06/16/2025</v>
       </c>
       <c r="B41" t="str">
-        <v>$109.45</v>
+        <v>$20,200.00</v>
       </c>
       <c r="C41" t="str">
-        <v>275 ZBA Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D41" t="str">
-        <v>ZBA CREDIT - SUB ACCOUNT FROM FROM ACCOUNT</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E41" t="str">
         <v>-</v>
@@ -3508,13 +3508,13 @@
         <v>06/23/2025</v>
       </c>
       <c r="B48" t="str">
-        <v>$80,000.00</v>
+        <v>$167.63</v>
       </c>
       <c r="C48" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D48" t="str">
-        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E48" t="str">
         <v>-</v>
@@ -3542,13 +3542,13 @@
         <v>06/23/2025</v>
       </c>
       <c r="B50" t="str">
-        <v>$167.63</v>
+        <v>$28,213.76</v>
       </c>
       <c r="C50" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D50" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
       </c>
       <c r="E50" t="str">
         <v>-</v>
@@ -3559,13 +3559,13 @@
         <v>06/23/2025</v>
       </c>
       <c r="B51" t="str">
-        <v>$409,648.80</v>
+        <v>$28,213.76</v>
       </c>
       <c r="C51" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D51" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
       </c>
       <c r="E51" t="str">
         <v>-</v>
@@ -3576,13 +3576,13 @@
         <v>06/23/2025</v>
       </c>
       <c r="B52" t="str">
-        <v>$28,213.76</v>
+        <v>$80,000.00</v>
       </c>
       <c r="C52" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D52" t="str">
-        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
+        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
       </c>
       <c r="E52" t="str">
         <v>-</v>
@@ -3593,13 +3593,13 @@
         <v>06/23/2025</v>
       </c>
       <c r="B53" t="str">
-        <v>$28,213.76</v>
+        <v>$409,648.80</v>
       </c>
       <c r="C53" t="str">
         <v>275 ZBA Credit</v>
       </c>
       <c r="D53" t="str">
-        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E53" t="str">
         <v>-</v>
@@ -3610,13 +3610,13 @@
         <v>06/24/2025</v>
       </c>
       <c r="B54" t="str">
-        <v>$8,435.86</v>
+        <v>$239.00</v>
       </c>
       <c r="C54" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D54" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E54" t="str">
         <v>-</v>
@@ -3627,13 +3627,13 @@
         <v>06/24/2025</v>
       </c>
       <c r="B55" t="str">
-        <v>$400,000.00</v>
+        <v>$8,435.86</v>
       </c>
       <c r="C55" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D55" t="str">
-        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E55" t="str">
         <v>-</v>
@@ -3644,7 +3644,7 @@
         <v>06/24/2025</v>
       </c>
       <c r="B56" t="str">
-        <v>$239.00</v>
+        <v>$122,239.57</v>
       </c>
       <c r="C56" t="str">
         <v>275 ZBA Credit</v>
@@ -3661,13 +3661,13 @@
         <v>06/24/2025</v>
       </c>
       <c r="B57" t="str">
-        <v>$122,239.57</v>
+        <v>$400,000.00</v>
       </c>
       <c r="C57" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D57" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
       </c>
       <c r="E57" t="str">
         <v>-</v>
@@ -3678,13 +3678,13 @@
         <v>06/25/2025</v>
       </c>
       <c r="B58" t="str">
-        <v>$130,000.00</v>
+        <v>$1,272.92</v>
       </c>
       <c r="C58" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D58" t="str">
-        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E58" t="str">
         <v>-</v>
@@ -3695,13 +3695,13 @@
         <v>06/25/2025</v>
       </c>
       <c r="B59" t="str">
-        <v>$1,272.92</v>
+        <v>$9,110.00</v>
       </c>
       <c r="C59" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D59" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
       </c>
       <c r="E59" t="str">
         <v>-</v>
@@ -3712,13 +3712,13 @@
         <v>06/25/2025</v>
       </c>
       <c r="B60" t="str">
-        <v>$9,110.00</v>
+        <v>$130,000.00</v>
       </c>
       <c r="C60" t="str">
-        <v>275 ZBA Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D60" t="str">
-        <v>TRANSFER FROM DEPOSIT SYSTEM ACCOUNT XXXXXX</v>
+        <v>REF# BBFFT FROM: SUNSET LAKE HEALTHCARE AND REHABIL ABA: BANK:OBI: TRANSFEROBI:OBI:</v>
       </c>
       <c r="E60" t="str">
         <v>-</v>
@@ -3746,13 +3746,13 @@
         <v>06/27/2025</v>
       </c>
       <c r="B62" t="str">
-        <v>$75,000.00</v>
+        <v>$1,410.91</v>
       </c>
       <c r="C62" t="str">
-        <v>195 Incoming Money Transfer</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D62" t="str">
-        <v>REF# BBFFT FROM: VENICE NH LLC ABA: BANK:</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E62" t="str">
         <v>-</v>
@@ -3780,13 +3780,13 @@
         <v>06/27/2025</v>
       </c>
       <c r="B64" t="str">
-        <v>$1,410.91</v>
+        <v>$74,000.00</v>
       </c>
       <c r="C64" t="str">
-        <v>275 ZBA Credit</v>
+        <v>206 Book Transfer Credit</v>
       </c>
       <c r="D64" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>REF L FUNDS TRANSFER FRMDEP XXXXX FROM</v>
       </c>
       <c r="E64" t="str">
         <v>-</v>
@@ -3797,13 +3797,13 @@
         <v>06/27/2025</v>
       </c>
       <c r="B65" t="str">
-        <v>$74,000.00</v>
+        <v>$75,000.00</v>
       </c>
       <c r="C65" t="str">
-        <v>206 Book Transfer Credit</v>
+        <v>195 Incoming Money Transfer</v>
       </c>
       <c r="D65" t="str">
-        <v>REF L FUNDS TRANSFER FRMDEP XXXXX FROM</v>
+        <v>REF# BBFFT FROM: VENICE NH LLC ABA: BANK:</v>
       </c>
       <c r="E65" t="str">
         <v>-</v>
@@ -3814,13 +3814,13 @@
         <v>06/30/2025</v>
       </c>
       <c r="B66" t="str">
-        <v>$11,764.73</v>
+        <v>$4,478.73</v>
       </c>
       <c r="C66" t="str">
-        <v>201 Individual Automatic Transfer Credit</v>
+        <v>275 ZBA Credit</v>
       </c>
       <c r="D66" t="str">
-        <v>SWEEP TRANSFER FROM</v>
+        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
       </c>
       <c r="E66" t="str">
         <v>-</v>
@@ -3831,13 +3831,13 @@
         <v>06/30/2025</v>
       </c>
       <c r="B67" t="str">
-        <v>$4,478.73</v>
+        <v>$11,764.73</v>
       </c>
       <c r="C67" t="str">
-        <v>275 ZBA Credit</v>
+        <v>201 Individual Automatic Transfer Credit</v>
       </c>
       <c r="D67" t="str">
-        <v>ZBA CREDIT - MASTER ACCOUNT FROM</v>
+        <v>SWEEP TRANSFER FROM</v>
       </c>
       <c r="E67" t="str">
         <v>-</v>
